--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tvlk\Email Sprint 3\Traveloka_DataAutomation_Performer_Email_S3\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D70580-CA4A-436A-B478-00D1A0B353C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418650B5-7386-485D-B3F7-2BD7933874D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="165" windowWidth="28800" windowHeight="15435" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -165,9 +165,6 @@
     <t>RPA_Moon_SenderName</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_Email</t>
-  </si>
-  <si>
     <t>Traveloka_DataAutomation</t>
   </si>
   <si>
@@ -183,21 +180,18 @@
     <t>EmailRawFolderName</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_UploadBucket</t>
-  </si>
-  <si>
     <t>RPA_Moon_Email_Date</t>
   </si>
   <si>
     <t>Email_Raw_Data</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_PathMailTemplate</t>
-  </si>
-  <si>
     <t>ConverterPath</t>
   </si>
   <si>
+    <t>RPA_Moon_PathExcel</t>
+  </si>
+  <si>
     <t>RPA_Moon_AutoRetryMax</t>
   </si>
   <si>
@@ -210,10 +204,16 @@
     <t>AutoRetryPostpone</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_PathExcel</t>
-  </si>
-  <si>
-    <t>[Dev] RPA_Moon_Cred_Gmail</t>
+    <t>RPA_Moon_Cred_Gmail</t>
+  </si>
+  <si>
+    <t>RPA_Moon_UploadBucket</t>
+  </si>
+  <si>
+    <t>RPA_Moon_PathMailTemplate</t>
+  </si>
+  <si>
+    <t>RPA_Moon_Email_S3</t>
   </si>
   <si>
     <t>RPA_Moon_AutoRetryMaxDay</t>
@@ -231,7 +231,7 @@
     <t>PathTabula</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_PathTabula</t>
+    <t>RPA_Moon_PathTabula</t>
   </si>
 </sst>
 </file>
@@ -655,7 +655,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -676,7 +676,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -684,34 +684,34 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2920,7 +2920,7 @@
         <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
@@ -2933,26 +2933,26 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
